--- a/review-results/复盘信息抓取-20261019.xlsx
+++ b/review-results/复盘信息抓取-20261019.xlsx
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>11664.658</v>
+        <v>11769.503</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>365.968</v>
+        <v>297.558</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -5190,14 +5190,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>999.802</v>
+        <v>1010.297</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>131.05</v>
+        <v>209.77</v>
       </c>
     </row>
     <row r="4">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>11769.503</v>
+        <v>14043.468</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>297.558</v>
+        <v>445.443</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5234,14 +5234,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1010.297</v>
+        <v>1110.421</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>209.77</v>
+        <v>403.54</v>
       </c>
     </row>
     <row r="5">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11769.503</v>
+        <v>13786.014</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>297.558</v>
+        <v>465.375</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1010.297</v>
+        <v>1176.16</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>209.77</v>
+        <v>415.64</v>
       </c>
     </row>
     <row r="6">
@@ -5301,14 +5301,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14043.468</v>
+        <v>13548.766</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>445.443</v>
+        <v>460.83</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -5322,14 +5322,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1110.421</v>
+        <v>1166.35</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>403.54</v>
+        <v>404.14</v>
       </c>
     </row>
     <row r="7">
@@ -5345,14 +5345,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>14043.468</v>
+        <v>13897.377</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>445.443</v>
+        <v>458.11</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -5366,14 +5366,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1110.421</v>
+        <v>1135.188</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>403.54</v>
+        <v>403.76</v>
       </c>
     </row>
     <row r="8">
@@ -5389,14 +5389,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>13786.014</v>
+        <v>15375.231</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>465.375</v>
+        <v>450.993</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5410,14 +5410,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1176.16</v>
+        <v>1486.371</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>415.64</v>
+        <v>488.3</v>
       </c>
     </row>
     <row r="9">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>08</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>13786.014</v>
+        <v>16794.135</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>465.375</v>
+        <v>473.138</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1176.16</v>
+        <v>1224.685</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>415.64</v>
+        <v>450.29</v>
       </c>
     </row>
     <row r="10">
@@ -5477,14 +5477,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13548.766</v>
+        <v>15571.013</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>460.83</v>
+        <v>231.17</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5498,14 +5498,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>09</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1166.35</v>
+        <v>1022.254</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>404.14</v>
+        <v>209.77</v>
       </c>
     </row>
     <row r="11">
@@ -5521,14 +5521,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13548.766</v>
+        <v>14593.087</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>460.83</v>
+        <v>107.335</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5542,14 +5542,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1166.35</v>
+        <v>1005.074</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>404.14</v>
+        <v>209.77</v>
       </c>
     </row>
     <row r="12">
@@ -5565,14 +5565,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>13897.377</v>
+        <v>15753.183</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>458.11</v>
+        <v>179.318</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5586,14 +5586,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1135.188</v>
+        <v>982.793</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>403.76</v>
+        <v>131.05</v>
       </c>
     </row>
     <row r="13">
@@ -5609,14 +5609,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>13897.377</v>
+        <v>16550.184</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>458.11</v>
+        <v>115.588</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -5630,14 +5630,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1135.188</v>
+        <v>984.1559999999999</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>403.76</v>
+        <v>131.05</v>
       </c>
     </row>
     <row r="14">
@@ -5653,14 +5653,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>15375.231</v>
+        <v>15949.6</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>450.993</v>
+        <v>116.148</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -5674,14 +5674,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>1486.371</v>
+        <v>899.922</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>488.3</v>
+        <v>89.36</v>
       </c>
     </row>
     <row r="15">
@@ -5697,14 +5697,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>15375.231</v>
+        <v>16365.591</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>450.993</v>
+        <v>237.138</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -5718,14 +5718,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1486.371</v>
+        <v>929.021</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>488.3</v>
+        <v>95.55</v>
       </c>
     </row>
     <row r="16">
@@ -5741,14 +5741,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>16794.135</v>
+        <v>15569.843</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>473.138</v>
+        <v>113.115</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -5762,14 +5762,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1224.685</v>
+        <v>951.514</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>450.29</v>
+        <v>125.72</v>
       </c>
     </row>
     <row r="17">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16794.135</v>
+        <v>13911.883</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>473.138</v>
+        <v>148.118</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -5806,14 +5806,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1224.685</v>
+        <v>1075.011</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>450.29</v>
+        <v>240.63</v>
       </c>
     </row>
     <row r="18">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>15571.013</v>
+        <v>14443.113</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>231.17</v>
+        <v>393.118</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -5850,14 +5850,14 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1022.254</v>
+        <v>1199.758</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>209.77</v>
+        <v>450.13</v>
       </c>
     </row>
     <row r="19">
@@ -5873,14 +5873,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15571.013</v>
+        <v>15882.519</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>231.17</v>
+        <v>460.988</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1022.254</v>
+        <v>1347.961</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>209.77</v>
+        <v>466.79</v>
       </c>
     </row>
     <row r="20">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>14593.087</v>
+        <v>15248.053</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>107.335</v>
+        <v>450.84</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -5938,14 +5938,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1005.074</v>
+        <v>1107.548</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>209.77</v>
+        <v>403.54</v>
       </c>
     </row>
     <row r="21">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14593.087</v>
+        <v>13831.364</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>107.335</v>
+        <v>284.715</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1005.074</v>
+        <v>982.849</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>209.77</v>
+        <v>131.05</v>
       </c>
     </row>
     <row r="22">
@@ -6005,14 +6005,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>15753.183</v>
+        <v>13967.546</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>179.318</v>
+        <v>246.59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -6026,11 +6026,11 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>982.793</v>
+        <v>987.116</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>131.05</v>
@@ -6049,14 +6049,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>15753.183</v>
+        <v>14465.204</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>179.318</v>
+        <v>284.973</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -6070,14 +6070,14 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>982.793</v>
+        <v>961.228</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>131.05</v>
+        <v>125.72</v>
       </c>
     </row>
     <row r="24">
@@ -6093,14 +6093,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>16550.184</v>
+        <v>12921.223</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>115.588</v>
+        <v>118.545</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -6114,11 +6114,11 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>984.1559999999999</v>
+        <v>975.466</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>131.05</v>
@@ -6137,14 +6137,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>16550.184</v>
+        <v>11923.289</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>115.588</v>
+        <v>112.15</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -6158,1069 +6158,13 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>984.1559999999999</v>
+        <v>961.832</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>15949.6</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>116.148</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>899.922</v>
-      </c>
-      <c r="L26" t="n">
-        <v>89.36</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>15949.6</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>116.148</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>899.922</v>
-      </c>
-      <c r="L27" t="n">
-        <v>89.36</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>16365.591</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>237.138</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>929.021</v>
-      </c>
-      <c r="L28" t="n">
-        <v>95.55</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>16365.591</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>237.138</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>929.021</v>
-      </c>
-      <c r="L29" t="n">
-        <v>95.55</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>15569.843</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>113.115</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>951.514</v>
-      </c>
-      <c r="L30" t="n">
-        <v>125.72</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>15569.843</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>113.115</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>951.514</v>
-      </c>
-      <c r="L31" t="n">
-        <v>125.72</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>13911.883</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>148.118</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>1075.011</v>
-      </c>
-      <c r="L32" t="n">
-        <v>240.63</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>13911.883</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>148.118</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>1075.011</v>
-      </c>
-      <c r="L33" t="n">
-        <v>240.63</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>14443.113</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>393.118</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1199.758</v>
-      </c>
-      <c r="L34" t="n">
-        <v>450.13</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>14443.113</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>393.118</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>1199.758</v>
-      </c>
-      <c r="L35" t="n">
-        <v>450.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>15882.519</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>460.988</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>1347.961</v>
-      </c>
-      <c r="L36" t="n">
-        <v>466.79</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>15882.519</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>460.988</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>1347.961</v>
-      </c>
-      <c r="L37" t="n">
-        <v>466.79</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>15248.053</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>450.84</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>1107.548</v>
-      </c>
-      <c r="L38" t="n">
-        <v>403.54</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>15248.053</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>450.84</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>1107.548</v>
-      </c>
-      <c r="L39" t="n">
-        <v>403.54</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>13831.364</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>284.715</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>982.849</v>
-      </c>
-      <c r="L40" t="n">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>13831.364</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>284.715</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>982.849</v>
-      </c>
-      <c r="L41" t="n">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>13967.546</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>246.59</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>987.116</v>
-      </c>
-      <c r="L42" t="n">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>13967.546</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>246.59</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>987.116</v>
-      </c>
-      <c r="L43" t="n">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>14465.204</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>284.973</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>961.228</v>
-      </c>
-      <c r="L44" t="n">
-        <v>125.72</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>14465.204</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>284.973</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>961.228</v>
-      </c>
-      <c r="L45" t="n">
-        <v>125.72</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>12921.223</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>118.545</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>975.466</v>
-      </c>
-      <c r="L46" t="n">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>12921.223</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>118.545</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>975.466</v>
-      </c>
-      <c r="L47" t="n">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>11923.289</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>112.15</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>961.832</v>
-      </c>
-      <c r="L48" t="n">
-        <v>125.72</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>现货实时交易价格曲线</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>11923.289</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>112.15</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>现货日前交易价格曲线</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>961.832</v>
-      </c>
-      <c r="L49" t="n">
         <v>125.72</v>
       </c>
     </row>
@@ -18347,7 +17291,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -18360,7 +17304,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
